--- a/analysis_results/c2a_rp_block2_distribution_20260810_v1/worker_facing_release/Task_Assignments_C2A_RP_Block2_English.xlsx
+++ b/analysis_results/c2a_rp_block2_distribution_20260810_v1/worker_facing_release/Task_Assignments_C2A_RP_Block2_English.xlsx
@@ -2,7 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block 2 Tasks" sheetId="1" r:id="R8ec56568786d4c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R9b00f13d5cb64fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W028" sheetId="2" r:id="R6c84e1ad538948f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W029" sheetId="3" r:id="R5471c0db808b401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W030" sheetId="4" r:id="R457d6017d9ea461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W031" sheetId="5" r:id="R34db8d5b95cc4b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W032" sheetId="6" r:id="R3def611c438d42c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W033" sheetId="7" r:id="R17546e62981248c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W034" sheetId="8" r:id="Rf7c31536169e4c8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W035" sheetId="9" r:id="R3d508f5aab844186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W036" sheetId="10" r:id="R902ba805bf8349b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W037" sheetId="11" r:id="Rbecb170b5d9f4afb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,20 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF203040"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -36,7 +35,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,70 +49,66 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD9EAF7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF5B9BD5"/>
+        <x:fgColor rgb="FFF8FAFC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFD9E2F3"/>
+        <x:color rgb="FFB8C6D1"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFD9E2F3"/>
+        <x:color rgb="FFB8C6D1"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFD9E2F3"/>
+        <x:color rgb="FFB8C6D1"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFD9E2F3"/>
+        <x:color rgb="FFB8C6D1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD5DEE5"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EnglishBlock2Assignments" displayName="EnglishBlock2Assignments" ref="A4:D14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="Worker ID"/>
-    <x:tableColumn id="2" name="Project"/>
-    <x:tableColumn id="3" name="Task 1"/>
-    <x:tableColumn id="4" name="Task 2"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -311,190 +306,395 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="41.25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="41.25" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>C2-A-RP Block 2 Task Assignments</x:v>
-      </x:c>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-      <x:c r="D1" s="2"/>
-    </x:row>
-    <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="5" t="str">
-        <x:v>Complete the two assigned tasks in Project E. Please do not work on tasks assigned to another worker.</x:v>
-      </x:c>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-    </x:row>
-    <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="9" t="str">
-        <x:v>Worker ID</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>Project</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>Task 1</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>Task 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="10" t="str">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="str">
-        <x:v>jtcxE69GiFV_f4dc4040df5a4f038dd2b35f2bb65266</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="str">
-        <x:v>pa4otMbVnkk_5d1adb544bb14217ba5ded2eb82cd8e3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="10" t="str">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C6" s="10" t="str">
-        <x:v>pRbA3pwrgk9_16beb21e65a84850a509972190038d0e</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="str">
-        <x:v>pRbA3pwrgk9_2a3810bc7ecc491e81ff1e8a17692ec1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="10" t="str">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="str">
-        <x:v>pa4otMbVnkk_f6005da79d2c43ba820db8124a4287d1</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="str">
-        <x:v>S9hNv5qa7GM_53d54b73e58940019b731673e65c1902</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="10" t="str">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C8" s="10" t="str">
-        <x:v>2t7WUuJeko7_7b017f053981438a9c075e599f2c5866</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="str">
-        <x:v>VFuaQ6m2Qom_5fb269a812f349b4bc2ad5dfac000b85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="10" t="str">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C9" s="10" t="str">
-        <x:v>zsNo4HB9uLZ_935e0f6088a54fba87990835d1997d9a</x:v>
-      </x:c>
-      <x:c r="D9" s="10" t="str">
-        <x:v>pRbA3pwrgk9_03de6e2562bb4f56a88db3ceb681af78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="10" t="str">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C10" s="10" t="str">
-        <x:v>pRbA3pwrgk9_285b697fed754f86a09602c93628cfb4</x:v>
-      </x:c>
-      <x:c r="D10" s="10" t="str">
-        <x:v>jtcxE69GiFV_67790605390f4d439c3c59395967ec84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C11" s="10" t="str">
-        <x:v>2t7WUuJeko7_7b017f053981438a9c075e599f2c5866</x:v>
-      </x:c>
-      <x:c r="D11" s="10" t="str">
-        <x:v>jtcxE69GiFV_67790605390f4d439c3c59395967ec84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="10" t="str">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C12" s="10" t="str">
-        <x:v>pa4otMbVnkk_fc4ee7e59f32491d9817b3a9a5b5e9b1</x:v>
-      </x:c>
-      <x:c r="D12" s="10" t="str">
-        <x:v>pRbA3pwrgk9_03de6e2562bb4f56a88db3ceb681af78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="10" t="str">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C13" s="10" t="str">
-        <x:v>jtcxE69GiFV_c90412ad99334d3aa7a1ec74d8e543a1</x:v>
-      </x:c>
-      <x:c r="D13" s="10" t="str">
-        <x:v>jtcxE69GiFV_67790605390f4d439c3c59395967ec84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="10" t="str">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B14" s="10" t="str">
-        <x:v>Project E (78)</x:v>
-      </x:c>
-      <x:c r="C14" s="10" t="str">
-        <x:v>jh4fc5c5qoQ_a59a3a61089343a8ba2834e7d3cd1066</x:v>
-      </x:c>
-      <x:c r="D14" s="10" t="str">
-        <x:v>S9hNv5qa7GM_53d54b73e58940019b731673e65c1902</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53daf7cd739c45bf"/>
-  </x:tableParts>
+    <x:col min="1" max="1" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Instructions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Use the sheet matching your worker ID.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>Complete the 2 tasks in Project F in order.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-012</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-006</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-002</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-004</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-006</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-008</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-010</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-012</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-012</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Project F-013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Project F-010</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>